--- a/data/satisfaction_detail/2026/6月/专业观众.xlsx
+++ b/data/satisfaction_detail/2026/6月/专业观众.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>9.960000000000001</v>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="10">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9.970000000000001</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.279999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.4</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="15">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.85</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>10</v>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>10</v>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.17</v>
+        <v>8.76</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>10</v>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="20">
